--- a/Aircraft.xlsx
+++ b/Aircraft.xlsx
@@ -5,17 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AMDOA506\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Personal\Obsidian\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD6342F-EDF6-442E-9538-1E3B61123A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F6F1BEF-244E-48E1-A77B-B845785B4E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>巡航重量</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -143,6 +144,54 @@
   </si>
   <si>
     <t>绿色单元格为输入，红色单元格为输出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞机重量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞机长度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巡航高度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巡航马赫数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>k1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>λ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -262,12 +311,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -281,6 +324,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -303,6 +352,1137 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$M$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>F</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$L$10:$L$50</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="41"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.37500000000000006</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.625</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.75000000000000011</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.87500000000000011</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.125</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.375</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.625</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.75</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.875</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.125</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.25</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.375</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6.75</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>15.250000000000002</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>23.75</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>28.000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>32.25</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>36.5</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>40.75</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>47.7</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>50.4</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>53.1</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>55.8</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>58.5</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>61.2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>63.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>66.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>69.3</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>72</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$M$10:$M$50</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="41"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.3E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.6E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.9000000000000025E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.32E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.6500000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.9800000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.3100000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.64E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.9700000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.1899999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.0800000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.9700000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.86E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.75E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.64E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.5300000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.4199999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.3100000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.4125000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.6249999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.8375000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3.0499999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3.2625000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3.4750000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3.6874999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>4.1124999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>4.3249999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>4.4600000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-2.7299999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-2.5949999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-2.46E-2</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-2.325E-2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-2.1899999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-2.0549999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-1.9200000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-1.7849999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-1.6500000000000001E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1418-4BF3-9197-37EC5B38D272}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="384265951"/>
+        <c:axId val="307941903"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="384265951"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="307941903"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="307941903"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="384265951"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>578642</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>135731</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>111917</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>21431</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="图表 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2913548F-AFFA-263C-7EBA-58753890D02E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -568,108 +1748,108 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U8"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:U50"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="2" width="9.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9.73046875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.9296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.46484375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.73046875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.86328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.73046875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.86328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.73046875" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.46484375" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.1328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.53125" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="9" style="2"/>
     <col min="21" max="21" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:19" ht="20.25" x14ac:dyDescent="0.45">
+      <c r="A1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="H2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="Q2" s="4" t="s">
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="Q2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="4" t="s">
         <v>14</v>
       </c>
       <c r="Q3" s="2" t="s">
@@ -682,47 +1862,47 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A4" s="3">
         <v>135000</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="3">
         <v>300.60000000000002</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="3">
         <v>1.8</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="3">
         <v>18000</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="4">
         <f>(A4*9.8)/(0.5*I4*H4^2*B4*2)</f>
         <v>0.12825545086648585</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="4">
         <f>C4*M4</f>
         <v>531.12508831632874</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="4">
         <f>J4/(287.05287*216.65)</f>
         <v>0.12164700015396786</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="4">
         <f>IF(L4&lt;=11000,
 101325*((288.15-0.0065*L4)/288.15)^(-9.80665/(287*-0.0065)),
 22632.0603973166*EXP(-9.80665*(L4-11000)/(287.05287*216.65))
 )</f>
         <v>7565.2274608934804</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="4">
         <f>IF(L4&lt;=11000,288.15-0.0065*L4,216.65)</f>
         <v>216.65</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="4">
         <f>6356766*(D4)/(6356766+D4)</f>
         <v>17949.174604997264</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="4">
         <f>SQRT(1.4*287.05287*K4)</f>
         <v>295.06949350907149</v>
       </c>
@@ -736,55 +1916,566 @@
         <v>288.14999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A8" s="3">
         <v>0.45</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="L9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="K10" s="2">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2">
+        <f t="shared" ref="L10:L20" si="0">0.5*$A$14*K10</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="2">
+        <f t="shared" ref="M10:M20" si="1">2*L10*$B$14/$A$14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="L11" s="2">
+        <f t="shared" si="0"/>
+        <v>0.125</v>
+      </c>
+      <c r="M11" s="2">
+        <f t="shared" si="1"/>
+        <v>3.3E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A12" s="2">
+        <v>135000</v>
+      </c>
+      <c r="B12" s="2">
+        <v>72</v>
+      </c>
+      <c r="C12" s="2">
+        <v>18000</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="K12" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="L12" s="2">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+      <c r="M12" s="2">
+        <f t="shared" si="1"/>
+        <v>6.6E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13" s="2">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="L13" s="2">
+        <f t="shared" si="0"/>
+        <v>0.37500000000000006</v>
+      </c>
+      <c r="M13" s="2">
+        <f t="shared" si="1"/>
+        <v>9.9000000000000025E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A14" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="B14" s="2">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="D14" s="2">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="K14" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="L14" s="2">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="M14" s="2">
+        <f t="shared" si="1"/>
+        <v>1.32E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="L15" s="2">
+        <f t="shared" si="0"/>
+        <v>0.625</v>
+      </c>
+      <c r="M15" s="2">
+        <f t="shared" si="1"/>
+        <v>1.6500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A16" s="2">
+        <v>45</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="K16" s="2">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="L16" s="2">
+        <f t="shared" si="0"/>
+        <v>0.75000000000000011</v>
+      </c>
+      <c r="M16" s="2">
+        <f t="shared" si="1"/>
+        <v>1.9800000000000005E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K17" s="2">
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="L17" s="2">
+        <f t="shared" si="0"/>
+        <v>0.87500000000000011</v>
+      </c>
+      <c r="M17" s="2">
+        <f t="shared" si="1"/>
+        <v>2.3100000000000002E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K18" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="L18" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M18" s="2">
+        <f t="shared" si="1"/>
+        <v>2.64E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K19" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="L19" s="2">
+        <f t="shared" si="0"/>
+        <v>1.125</v>
+      </c>
+      <c r="M19" s="2">
+        <f t="shared" si="1"/>
+        <v>2.9700000000000004E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K20" s="2">
+        <v>1</v>
+      </c>
+      <c r="L20" s="2">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="M20" s="2">
+        <f t="shared" si="1"/>
+        <v>3.3000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="L21" s="2">
+        <f t="shared" ref="L21:L30" si="2">0.5*$A$14+0.5*K11*$A$14</f>
+        <v>1.375</v>
+      </c>
+      <c r="M21" s="2">
+        <f t="shared" ref="M21:M30" si="3">$C$14*(2*L21/$A$14-1)-$B$14*(2*L21/$A$14-2)</f>
+        <v>3.1899999999999998E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="L22" s="2">
+        <f t="shared" si="2"/>
+        <v>1.5</v>
+      </c>
+      <c r="M22" s="2">
+        <f t="shared" si="3"/>
+        <v>3.0800000000000001E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="L23" s="2">
+        <f t="shared" si="2"/>
+        <v>1.625</v>
+      </c>
+      <c r="M23" s="2">
+        <f t="shared" si="3"/>
+        <v>2.9700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="L24" s="2">
+        <f t="shared" si="2"/>
+        <v>1.75</v>
+      </c>
+      <c r="M24" s="2">
+        <f t="shared" si="3"/>
+        <v>2.86E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="L25" s="2">
+        <f t="shared" si="2"/>
+        <v>1.875</v>
+      </c>
+      <c r="M25" s="2">
+        <f t="shared" si="3"/>
+        <v>2.75E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="L26" s="2">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="M26" s="2">
+        <f t="shared" si="3"/>
+        <v>2.64E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="L27" s="2">
+        <f t="shared" si="2"/>
+        <v>2.125</v>
+      </c>
+      <c r="M27" s="2">
+        <f t="shared" si="3"/>
+        <v>2.5300000000000003E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="L28" s="2">
+        <f t="shared" si="2"/>
+        <v>2.25</v>
+      </c>
+      <c r="M28" s="2">
+        <f t="shared" si="3"/>
+        <v>2.4199999999999999E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="L29" s="2">
+        <f t="shared" si="2"/>
+        <v>2.375</v>
+      </c>
+      <c r="M29" s="2">
+        <f t="shared" si="3"/>
+        <v>2.3100000000000002E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="L30" s="2">
+        <f t="shared" si="2"/>
+        <v>2.5</v>
+      </c>
+      <c r="M30" s="2">
+        <f t="shared" si="3"/>
+        <v>2.1999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="L31" s="2">
+        <f>$A$14+K11*($A$16-$A$14)</f>
+        <v>6.75</v>
+      </c>
+      <c r="M31" s="2">
+        <f>$D$14*(L31-$A$14)+$C$14</f>
+        <v>2.4125000000000001E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="L32" s="2">
+        <f t="shared" ref="L32:L40" si="4">$A$14+K12*($A$16-$A$14)</f>
+        <v>11</v>
+      </c>
+      <c r="M32" s="2">
+        <f t="shared" ref="M32:M41" si="5">$D$14*(L32-$A$14)+$C$14</f>
+        <v>2.6249999999999999E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="12:13" x14ac:dyDescent="0.4">
+      <c r="L33" s="2">
+        <f t="shared" si="4"/>
+        <v>15.250000000000002</v>
+      </c>
+      <c r="M33" s="2">
+        <f t="shared" si="5"/>
+        <v>2.8375000000000001E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="12:13" x14ac:dyDescent="0.4">
+      <c r="L34" s="2">
+        <f t="shared" si="4"/>
+        <v>19.5</v>
+      </c>
+      <c r="M34" s="2">
+        <f t="shared" si="5"/>
+        <v>3.0499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="12:13" x14ac:dyDescent="0.4">
+      <c r="L35" s="2">
+        <f t="shared" si="4"/>
+        <v>23.75</v>
+      </c>
+      <c r="M35" s="2">
+        <f t="shared" si="5"/>
+        <v>3.2625000000000001E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="12:13" x14ac:dyDescent="0.4">
+      <c r="L36" s="2">
+        <f t="shared" si="4"/>
+        <v>28.000000000000004</v>
+      </c>
+      <c r="M36" s="2">
+        <f t="shared" si="5"/>
+        <v>3.4750000000000003E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="12:13" x14ac:dyDescent="0.4">
+      <c r="L37" s="2">
+        <f t="shared" si="4"/>
+        <v>32.25</v>
+      </c>
+      <c r="M37" s="2">
+        <f t="shared" si="5"/>
+        <v>3.6874999999999998E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="12:13" x14ac:dyDescent="0.4">
+      <c r="L38" s="2">
+        <f t="shared" si="4"/>
+        <v>36.5</v>
+      </c>
+      <c r="M38" s="2">
+        <f t="shared" si="5"/>
+        <v>3.9E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="12:13" x14ac:dyDescent="0.4">
+      <c r="L39" s="2">
+        <f t="shared" si="4"/>
+        <v>40.75</v>
+      </c>
+      <c r="M39" s="2">
+        <f t="shared" si="5"/>
+        <v>4.1124999999999995E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="12:13" x14ac:dyDescent="0.4">
+      <c r="L40" s="2">
+        <f t="shared" si="4"/>
+        <v>45</v>
+      </c>
+      <c r="M40" s="2">
+        <f t="shared" si="5"/>
+        <v>4.3249999999999997E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="12:13" x14ac:dyDescent="0.4">
+      <c r="L41" s="2">
+        <f>$A$16+K11*($B$12-$A$16)</f>
+        <v>47.7</v>
+      </c>
+      <c r="M41" s="2">
+        <f t="shared" si="5"/>
+        <v>4.4600000000000001E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="12:13" x14ac:dyDescent="0.4">
+      <c r="L42" s="2">
+        <f t="shared" ref="L42:L50" si="6">$A$16+K12*($B$12-$A$16)</f>
+        <v>50.4</v>
+      </c>
+      <c r="M42" s="2">
+        <f>$D$14*(L42-$A$16)-$B$16</f>
+        <v>-2.7299999999999998E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="12:13" x14ac:dyDescent="0.4">
+      <c r="L43" s="2">
+        <f t="shared" si="6"/>
+        <v>53.1</v>
+      </c>
+      <c r="M43" s="2">
+        <f t="shared" ref="M43:M50" si="7">$D$14*(L43-$A$16)-$B$16</f>
+        <v>-2.5949999999999997E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="12:13" x14ac:dyDescent="0.4">
+      <c r="L44" s="2">
+        <f t="shared" si="6"/>
+        <v>55.8</v>
+      </c>
+      <c r="M44" s="2">
+        <f t="shared" si="7"/>
+        <v>-2.46E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="12:13" x14ac:dyDescent="0.4">
+      <c r="L45" s="2">
+        <f t="shared" si="6"/>
+        <v>58.5</v>
+      </c>
+      <c r="M45" s="2">
+        <f t="shared" si="7"/>
+        <v>-2.325E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="12:13" x14ac:dyDescent="0.4">
+      <c r="L46" s="2">
+        <f t="shared" si="6"/>
+        <v>61.2</v>
+      </c>
+      <c r="M46" s="2">
+        <f t="shared" si="7"/>
+        <v>-2.1899999999999996E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="12:13" x14ac:dyDescent="0.4">
+      <c r="L47" s="2">
+        <f t="shared" si="6"/>
+        <v>63.900000000000006</v>
+      </c>
+      <c r="M47" s="2">
+        <f t="shared" si="7"/>
+        <v>-2.0549999999999995E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="12:13" x14ac:dyDescent="0.4">
+      <c r="L48" s="2">
+        <f t="shared" si="6"/>
+        <v>66.599999999999994</v>
+      </c>
+      <c r="M48" s="2">
+        <f t="shared" si="7"/>
+        <v>-1.9200000000000002E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="12:13" x14ac:dyDescent="0.4">
+      <c r="L49" s="2">
+        <f t="shared" si="6"/>
+        <v>69.3</v>
+      </c>
+      <c r="M49" s="2">
+        <f t="shared" si="7"/>
+        <v>-1.7849999999999998E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="12:13" x14ac:dyDescent="0.4">
+      <c r="L50" s="2">
+        <f t="shared" si="6"/>
+        <v>72</v>
+      </c>
+      <c r="M50" s="2">
+        <f t="shared" si="7"/>
+        <v>-1.6500000000000001E-2</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -796,5 +2487,6 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>